--- a/InputData/dist-heat/BFoHfC/BAU Fraction of Heat from CHP.xlsx
+++ b/InputData/dist-heat/BFoHfC/BAU Fraction of Heat from CHP.xlsx
@@ -1,27 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipI\InputData\dist-heat\BFoHfC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\dist-heat\BFoHfC\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63FCB5D-8F9F-49EF-AD71-603A0D1EA1D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="45" windowWidth="23955" windowHeight="11310"/>
+    <workbookView xWindow="32625" yWindow="2040" windowWidth="24900" windowHeight="14490" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
     <sheet name="BFoHfC" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>BFoHfC BAU Fraction of Heat from CHP</t>
   </si>
@@ -123,12 +137,18 @@
   </si>
   <si>
     <t>Fraction of Heat from CHP (dimensionless)</t>
+  </si>
+  <si>
+    <t>green hydrogen</t>
+  </si>
+  <si>
+    <t>low carbon hydrogen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
@@ -189,10 +209,9 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -201,7 +220,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -231,9 +250,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -271,9 +290,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -308,7 +327,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -343,7 +362,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -516,19 +535,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="47.7109375" customWidth="1"/>
+    <col min="2" max="2" width="47.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -536,57 +555,57 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" s="2">
         <v>2014</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -598,31 +617,31 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" customWidth="1"/>
-    <col min="3" max="3" width="32.140625" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" customWidth="1"/>
+    <col min="1" max="1" width="19.54296875" customWidth="1"/>
+    <col min="2" max="2" width="21.54296875" customWidth="1"/>
+    <col min="3" max="3" width="32.1796875" customWidth="1"/>
+    <col min="4" max="4" width="22.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -636,7 +655,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -650,28 +669,28 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
         <f>((C2/B2)*D2+(C3/B3)*D3)/SUM(D2:D3)</f>
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -682,131 +701,131 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AK11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AK13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.28515625" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" customWidth="1"/>
+    <col min="1" max="1" width="25.26953125" customWidth="1"/>
+    <col min="2" max="2" width="9.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:37" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="7">
+      <c r="B1" s="6">
         <v>2015</v>
       </c>
       <c r="C1">
         <v>2016</v>
       </c>
-      <c r="D1" s="7">
+      <c r="D1" s="6">
         <v>2017</v>
       </c>
       <c r="E1">
         <v>2018</v>
       </c>
-      <c r="F1" s="7">
+      <c r="F1" s="6">
         <v>2019</v>
       </c>
       <c r="G1">
         <v>2020</v>
       </c>
-      <c r="H1" s="7">
+      <c r="H1" s="6">
         <v>2021</v>
       </c>
       <c r="I1">
         <v>2022</v>
       </c>
-      <c r="J1" s="7">
+      <c r="J1" s="6">
         <v>2023</v>
       </c>
       <c r="K1">
         <v>2024</v>
       </c>
-      <c r="L1" s="7">
+      <c r="L1" s="6">
         <v>2025</v>
       </c>
       <c r="M1">
         <v>2026</v>
       </c>
-      <c r="N1" s="7">
+      <c r="N1" s="6">
         <v>2027</v>
       </c>
       <c r="O1">
         <v>2028</v>
       </c>
-      <c r="P1" s="7">
+      <c r="P1" s="6">
         <v>2029</v>
       </c>
       <c r="Q1">
         <v>2030</v>
       </c>
-      <c r="R1" s="7">
+      <c r="R1" s="6">
         <v>2031</v>
       </c>
       <c r="S1">
         <v>2032</v>
       </c>
-      <c r="T1" s="7">
+      <c r="T1" s="6">
         <v>2033</v>
       </c>
       <c r="U1">
         <v>2034</v>
       </c>
-      <c r="V1" s="7">
+      <c r="V1" s="6">
         <v>2035</v>
       </c>
       <c r="W1">
         <v>2036</v>
       </c>
-      <c r="X1" s="7">
+      <c r="X1" s="6">
         <v>2037</v>
       </c>
       <c r="Y1">
         <v>2038</v>
       </c>
-      <c r="Z1" s="7">
+      <c r="Z1" s="6">
         <v>2039</v>
       </c>
       <c r="AA1">
         <v>2040</v>
       </c>
-      <c r="AB1" s="7">
+      <c r="AB1" s="6">
         <v>2041</v>
       </c>
       <c r="AC1">
         <v>2042</v>
       </c>
-      <c r="AD1" s="7">
+      <c r="AD1" s="6">
         <v>2043</v>
       </c>
       <c r="AE1">
         <v>2044</v>
       </c>
-      <c r="AF1" s="7">
+      <c r="AF1" s="6">
         <v>2045</v>
       </c>
       <c r="AG1">
         <v>2046</v>
       </c>
-      <c r="AH1" s="7">
+      <c r="AH1" s="6">
         <v>2047</v>
       </c>
       <c r="AI1">
         <v>2048</v>
       </c>
-      <c r="AJ1" s="7">
+      <c r="AJ1" s="6">
         <v>2049</v>
       </c>
       <c r="AK1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -955,7 +974,7 @@
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1104,7 +1123,7 @@
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1253,7 +1272,7 @@
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1402,7 +1421,7 @@
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -1551,7 +1570,7 @@
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1700,7 +1719,7 @@
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1849,7 +1868,7 @@
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1998,7 +2017,7 @@
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -2147,7 +2166,7 @@
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -2292,6 +2311,304 @@
         <v>0.50623017079495658</v>
       </c>
       <c r="AK11">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="C12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="D12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="E12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="F12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="G12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="H12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="I12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="J12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="K12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="L12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="M12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="N12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="O12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="P12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="Q12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="R12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="S12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="T12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="U12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="V12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="W12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="X12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="Y12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="Z12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AA12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AB12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AC12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AD12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AE12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AF12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AG12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AH12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AI12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AJ12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AK12">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="C13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="D13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="E13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="F13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="G13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="H13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="I13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="J13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="K13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="L13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="M13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="N13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="O13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="P13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="Q13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="R13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="S13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="T13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="U13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="V13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="W13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="X13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="Y13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="Z13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AA13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AB13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AC13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AD13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AE13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AF13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AG13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AH13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AI13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AJ13">
+        <f>Data!$A$6</f>
+        <v>0.50623017079495658</v>
+      </c>
+      <c r="AK13">
         <f>Data!$A$6</f>
         <v>0.50623017079495658</v>
       </c>

--- a/InputData/dist-heat/BFoHfC/BAU Fraction of Heat from CHP.xlsx
+++ b/InputData/dist-heat/BFoHfC/BAU Fraction of Heat from CHP.xlsx
@@ -1,41 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\dist-heat\BFoHfC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipI\InputData\dist-heat\BFoHfC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63FCB5D-8F9F-49EF-AD71-603A0D1EA1D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32625" yWindow="2040" windowWidth="24900" windowHeight="14490" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="45" windowWidth="23955" windowHeight="11310"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
     <sheet name="BFoHfC" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>BFoHfC BAU Fraction of Heat from CHP</t>
   </si>
@@ -137,18 +123,12 @@
   </si>
   <si>
     <t>Fraction of Heat from CHP (dimensionless)</t>
-  </si>
-  <si>
-    <t>green hydrogen</t>
-  </si>
-  <si>
-    <t>low carbon hydrogen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
@@ -209,9 +189,10 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -220,7 +201,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -250,9 +231,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -290,9 +271,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -327,7 +308,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -362,7 +343,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -535,19 +516,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="47.7265625" customWidth="1"/>
+    <col min="2" max="2" width="47.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -555,57 +536,57 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B4" s="2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="3">
         <v>2014</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -617,31 +598,31 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.54296875" customWidth="1"/>
-    <col min="2" max="2" width="21.54296875" customWidth="1"/>
-    <col min="3" max="3" width="32.1796875" customWidth="1"/>
-    <col min="4" max="4" width="22.54296875" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
+    <col min="3" max="3" width="32.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -655,7 +636,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -669,28 +650,28 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="5">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
         <f>((C2/B2)*D2+(C3/B3)*D3)/SUM(D2:D3)</f>
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -701,131 +682,131 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AK13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AK11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.26953125" customWidth="1"/>
-    <col min="2" max="2" width="9.453125" customWidth="1"/>
+    <col min="1" max="1" width="25.28515625" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:37" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="6">
+      <c r="B1" s="7">
         <v>2015</v>
       </c>
       <c r="C1">
         <v>2016</v>
       </c>
-      <c r="D1" s="6">
+      <c r="D1" s="7">
         <v>2017</v>
       </c>
       <c r="E1">
         <v>2018</v>
       </c>
-      <c r="F1" s="6">
+      <c r="F1" s="7">
         <v>2019</v>
       </c>
       <c r="G1">
         <v>2020</v>
       </c>
-      <c r="H1" s="6">
+      <c r="H1" s="7">
         <v>2021</v>
       </c>
       <c r="I1">
         <v>2022</v>
       </c>
-      <c r="J1" s="6">
+      <c r="J1" s="7">
         <v>2023</v>
       </c>
       <c r="K1">
         <v>2024</v>
       </c>
-      <c r="L1" s="6">
+      <c r="L1" s="7">
         <v>2025</v>
       </c>
       <c r="M1">
         <v>2026</v>
       </c>
-      <c r="N1" s="6">
+      <c r="N1" s="7">
         <v>2027</v>
       </c>
       <c r="O1">
         <v>2028</v>
       </c>
-      <c r="P1" s="6">
+      <c r="P1" s="7">
         <v>2029</v>
       </c>
       <c r="Q1">
         <v>2030</v>
       </c>
-      <c r="R1" s="6">
+      <c r="R1" s="7">
         <v>2031</v>
       </c>
       <c r="S1">
         <v>2032</v>
       </c>
-      <c r="T1" s="6">
+      <c r="T1" s="7">
         <v>2033</v>
       </c>
       <c r="U1">
         <v>2034</v>
       </c>
-      <c r="V1" s="6">
+      <c r="V1" s="7">
         <v>2035</v>
       </c>
       <c r="W1">
         <v>2036</v>
       </c>
-      <c r="X1" s="6">
+      <c r="X1" s="7">
         <v>2037</v>
       </c>
       <c r="Y1">
         <v>2038</v>
       </c>
-      <c r="Z1" s="6">
+      <c r="Z1" s="7">
         <v>2039</v>
       </c>
       <c r="AA1">
         <v>2040</v>
       </c>
-      <c r="AB1" s="6">
+      <c r="AB1" s="7">
         <v>2041</v>
       </c>
       <c r="AC1">
         <v>2042</v>
       </c>
-      <c r="AD1" s="6">
+      <c r="AD1" s="7">
         <v>2043</v>
       </c>
       <c r="AE1">
         <v>2044</v>
       </c>
-      <c r="AF1" s="6">
+      <c r="AF1" s="7">
         <v>2045</v>
       </c>
       <c r="AG1">
         <v>2046</v>
       </c>
-      <c r="AH1" s="6">
+      <c r="AH1" s="7">
         <v>2047</v>
       </c>
       <c r="AI1">
         <v>2048</v>
       </c>
-      <c r="AJ1" s="6">
+      <c r="AJ1" s="7">
         <v>2049</v>
       </c>
       <c r="AK1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -974,7 +955,7 @@
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1123,7 +1104,7 @@
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1272,7 +1253,7 @@
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -1421,7 +1402,7 @@
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -1570,7 +1551,7 @@
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1719,7 +1700,7 @@
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1868,7 +1849,7 @@
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -2017,7 +1998,7 @@
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -2166,7 +2147,7 @@
         <v>0.50623017079495658</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -2311,304 +2292,6 @@
         <v>0.50623017079495658</v>
       </c>
       <c r="AK11">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="C12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="D12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="E12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="F12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="G12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="H12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="I12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="J12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="K12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="L12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="M12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="N12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="O12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="P12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="Q12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="R12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="S12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="T12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="U12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="V12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="W12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="X12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="Y12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="Z12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AA12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AB12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AC12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AD12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AE12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AF12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AG12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AH12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AI12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AJ12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AK12">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-    </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="C13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="D13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="E13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="F13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="G13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="H13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="I13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="J13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="K13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="L13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="M13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="N13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="O13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="P13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="Q13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="R13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="S13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="T13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="U13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="V13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="W13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="X13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="Y13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="Z13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AA13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AB13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AC13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AD13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AE13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AF13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AG13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AH13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AI13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AJ13">
-        <f>Data!$A$6</f>
-        <v>0.50623017079495658</v>
-      </c>
-      <c r="AK13">
         <f>Data!$A$6</f>
         <v>0.50623017079495658</v>
       </c>
